--- a/text-content.xlsx
+++ b/text-content.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,7 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +480,7 @@
           <t>In Progress</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,6 +513,7 @@
           <t>Backlog</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -540,9 +543,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
+          <t>Pending"""</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    output_filename="test-strategy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/text-content.xlsx
+++ b/text-content.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,132 +434,39 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Priority\nAuthentication</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>US-001</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>US-001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>Login Page</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Create user login screen with email and password fields</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>High\nDashboard</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>US-002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Password Reset</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Implement forgot password workflow via email verification</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>User Stats</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US-003</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>User Stats</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Display active session counts and user metrics on main dashboard</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Pending"""</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    output_filename="test-strategy</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/text-content.xlsx
+++ b/text-content.xlsx
@@ -413,60 +413,1873 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>User Story ID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Priority\nAuthentication</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>US-001</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Login Page</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>High\nDashboard</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>US-002</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>User Stats</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>User Guide – Text File to Excel Conversion Workflow</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workflow documentation for text file to excel format normalizer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. Overview</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>This document provides a comprehensive user guide for the Text File to Excel Conversion Workflow. The workflow is designed to automate the extraction</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> transformation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> and conversion of structured or semi-structured text file data into Microsoft Excel format.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2. Workflow Details</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Workflow Name: Text to Excel Conversion</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Workflow Purpose: Convert input text files into formatted Excel spreadsheets</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Workflow Type: Automated Data Transformation Workflow</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Supported File Formats: .txt (customizable)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Output Format: Microsoft Excel (xlsx) (downloadable)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Execution Mode: Manual</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Expected Output: Structured Excel workbook with mapped columns and formatted data</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Workflow ID</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Workflow Name</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Workflow Actions</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Input</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Output</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	17104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Text to Excel Conversion 2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Convert input text files into formatted Excel spreadsheets</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Text File</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	.xlsx document</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3. Agent Details</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Agent Name: Text To Excel Transformation Agent</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent Description: This agent restructures unstructured or semi-structured text into clean Excel spreadsheets and provides users with a direct download link. </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execution Permissions: Read/Write access to source and destination folders in GitHub.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Monitoring Capability: Workflow execution logs and alert notifications</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Agent Name</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Mapped Workflow ID</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Actions</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Outputs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Tools Used</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Text To Excel Transformation Agent</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	17104</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	· File extraction and conversion</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	.xlsx document</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Text-to-Excel Generator</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	NA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4. Tool Details</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tool Name: Text-to-Excel Generator</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Primary Function: Converts raw text content into structured Excel spreadsheets dynamically.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Core Processing Engine: Uses Pandas DataFrame Transformation and OpenPyXL Excel generation.</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dynamic Header Detection: Automatically identifies delimiters such as pipe (|) and comma (</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>).</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>JSON Parsing Capability: Supports valid and malformed JSON structure recovery using heuristic repair logic.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Fallback Extraction Logic: Uses regex-based key-value extraction when standard JSON parsing fails.</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Multi-line Record Handling: Merges broken or wrapped text lines into the correct data rows.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Schema Matrix Normalization: Dynamically aligns parent-child row structures into tabular format.</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GitHub Integration: Uploads generated Excel files directly into a specified GitHub repository using GitHub REST API.</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Authentication Method: Uses GitHub Personal Access Token (PAT) for secure repository access.</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Supported Output Format: Microsoft Excel (.xlsx).</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Error Handling: Detects empty content</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> invalid layouts</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GitHub upload failures</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> and transformation exceptions.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Libraries Used: Pandas</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Requests</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OpenPyXL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pydantic</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Base64</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Regex (re)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Logging Utility: Captures execution logs and error details</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>5. Input Parameters</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>The following parameters are required before executing the workflow:</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Parameter</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Description</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Example</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Input text file</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Text file input file to be uploaded</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	data.txt uploaded as workflow input</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	GitHub token</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Access token for GitHub</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	ghp_L3wDyRoieUYLZ49hPKt</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	GitHub Repo Owner</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Owner name for the GitHub repo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	NavneetBN47</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	GitHub Repo Name</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Repository name</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	testX</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Output file Name</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Required name for the downloadable excel file</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Testcases (no suffix required)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6. Prerequisites</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AAVA int 2.0 access </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Access to Quality Engineering realm.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>GitHub repository setup.</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>User must have access permissions to input/output directories.</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Microsoft Excel or compatible spreadsheet software should be available for validation.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7. Execution Steps</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Place the source text file in the configured input directory of the workflow.</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Provide required input parameters and execute.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Monitor execution logs for successful completion.</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Verify generated Excel output by downloading from the URL provided in the workflow output.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>8. Error Handling &amp; Troubleshooting</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Invalid file format – Ensure the source file is supported</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Permission denied – Verify folder access permissions.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Empty output file – Validate source file contents.</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Workflow failure – Review execution logs for detailed error messages</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Common failure RCA – Ensure tool attachment in agent</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> verify repository access and token expiry.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>9. Example Execution Details</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Execution ID : 740e7f859-3ff9-464a-aded-8c25e077c353</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Execution logs : AAVA Launchpad – AI Agent Platform by Ascendion</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input file : </t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Output file : </t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>testcases delimited.txt</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Scenario ID|Scenario Title|Test Case ID|Test Case Title|Preconditions|Test Type|Automation Feasible|Test Data|Step #|Test Step Description|Expected Result</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TC001|US32275|Plan Recommendation|Verify side-by-side plan comparison|User is logged into the CareSource enrollment portal and has completed the health needs questionnaire|Functional|Yes|User with completed profile and at least two recommended plans|1|Navigate to plan recommendation page|System displays side-by-side comparison of at least two plans highlighting premiums</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> deductibles</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> co-pays</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> out-of-pocket maximums</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> and coverage for specified medications and doctors</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>||||||||2|Review plan features and select a plan|Selected plan is highlighted and user can proceed to enrollment</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TC002|US32275|Plan Recommendation|Verify navigation to enrollment after plan selection|User is on the plan comparison page|Functional|Yes|User with at least one recommended plan|1|Select a plan and click 'Enroll'|System transitions to the enrollment process with the chosen plan pre-selected</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TC003|US32275|Plan Recommendation|Negative - No recommended plans|User has completed health needs but no plans match criteria|Negative|Yes|User with uncommon criteria resulting in no matches|1|Navigate to plan recommendation page|System displays a message: "No plans match your criteria. Please adjust your preferences."</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TC004|US32275|Plan Recommendation|Edge - Maximum number of plans|User qualifies for 10+ plans|Edge|Yes|User with broad criteria resulting in maximum recommendations|1|Navigate to plan recommendation page|System displays all recommended plans in a scrollable</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> readable format without UI breakage</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TC005|US32274|Plan Personalization|Verify member can input medications and providers|User is authenticated|Functional|Yes|Medication: Metformin 500mg</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Provider: Dr. Smith|1|Navigate to health needs input page|System displays input fields for medications and providers</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>||||||||2|Enter medication and provider information and submit|System accepts input</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> validates data</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> and confirms successful entry</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TC006|US32274|Plan Personalization|Verify financial preference input|User is authenticated|Functional|Yes|Premium: $200</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Deductible: $1000</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OOP Max: $5000|1|Navigate to financial preferences section|System displays fields for premium</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> deductible</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> and out-of-pocket maximum</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>||||||||2|Enter preferences and submit|System saves preferences and updates recommendation criteria</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TC007|US32274|Plan Personalization|Negative - Invalid medication entry|User is authenticated|Negative|Yes|Medication: "" (blank entry)|1|Leave medication field blank and submit|System displays error: "Medication name required"</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TC008|US32274|Plan Personalization|Edge - Large medication list|User is authenticated|Edge|Yes|Medication: 20+ entries|1|Enter 20+ medications and submit|System accepts all entries and processes recommendations without error</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TC009|US32273|Guided Enrollment|Verify guided workflow for plan selection|User is a prospective member|Functional|Yes|Health: Asthma</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PCP: Dr. Lee</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Premium: $150|1|Start guided enrollment|System prompts for health data</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> provider</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> and financial preferences in sequence</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>||||||||2|Complete all steps and submit|System generates and displays personalized plan recommendations with comparison tool</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TC010|US32273|Guided Enrollment|Negative - Missing required fields|User is a prospective member|Negative|Yes|Omit required health data|1|Attempt to proceed without entering all required fields|System displays validation errors for missing fields</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TC011|US32273|Guided Enrollment|Edge - Extreme cost preferences|User is a prospective member|Edge|Yes|Premium: $0</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Deductible: $0|1|Enter extreme values and submit|System processes and displays only plans meeting criteria</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> or a message if none available</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TC012|US31822|Demographic Input|Verify demographic and health needs input|User is a prospective member|Functional|Yes|Age: 40</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Location: OH</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Doctor: Dr. Adams</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Medication: Lisinopril|1|Navigate to demographic input page|System displays fields for age</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> location</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> doctors</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> medications</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>||||||||2|Enter data and submit|System validates and accepts input</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> proceeding to recommendations</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TC013|US31822|Demographic Input|Negative - Invalid age|User is a prospective member|Negative|Yes|Age: -1|1|Enter invalid age and submit|System displays error: "Invalid age"</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TC014|US31822|Demographic Input|Edge - Maximum field length|User is a prospective member|Edge|Yes|Doctor name: 100+ characters|1|Enter maximum length for doctor name and submit|System accepts or displays appropriate error without crashing</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TC015|US32306|Profile|Verify profile view|User is logged in|Functional|Yes|User with profile data|1|Navigate to profile page|System displays correct profile information</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TC016|US32307|Settings|Verify settings update|User is logged in|Functional|Yes|New notification preference|1|Go to settings</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> change preference</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> save|System updates and confirms setting change</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TC017|US32308|Transaction History|Verify transaction history view|User is logged in|Functional|Yes|User with transaction history|1|Navigate to transaction history|System displays all past transactions</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TC018|US32309|Search and Filter|Verify data search and filter|User is logged in|Functional|Yes|Search: "Diabetes"</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Filter: Date range|1|Enter search term and filter|System returns correct filtered data</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TC019|US32310|Export Reports|Verify report export|User is logged in|Functional|Yes|Report: Claims|1|Click export on claims report|System downloads report in selected format</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TC020|US32311|User Permissions|Verify permission management|Admin user logged in|Functional|Yes|Assign 'Editor' to user X|1|Navigate to permissions</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> assign role|System saves and reflects new permission</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TC021|US32312|System Logs|Verify system log view|Admin user logged in|Functional|Yes|Any log record|1|Navigate to system logs|System displays logs with timestamp</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> user</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> action</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TC022|US32304|Password Reset|Verify password reset|User on login page|Functional|Yes|Registered email|1|Click 'Forgot Password'</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> enter email|System sends reset link to email</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TC023|US32305|Two-Factor Authentication|Verify 2FA enablement|User is logged in|Functional|Yes|Valid phone number|1|Navigate to security</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> enable 2FA|System sends code and confirms setup</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TC024|US32303|Login|Verify email login|User is registered|Functional|Yes|Valid email/password|1|Enter credentials</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> click login|System authenticates and redirects to dashboard</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TC025|US32983|NEW STORY TETS|Basic smoke test|System available|Functional|Yes|N/A|1|Access feature|Feature loads without error</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TC026|US32744|member 1|Basic smoke test|System available|Functional|Yes|N/A|1|Access feature|Feature loads without error</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/text-content.xlsx
+++ b/text-content.xlsx
@@ -413,1873 +413,2084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:B258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>User Guide – Text File to Excel Conversion Workflow</t>
+          <t>Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: EOB Document Generation - Variant 23 	 Id: TC1371 	 Description: Verify system handles invalid or missing data during EOB Document Generation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for EOB Document Generation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Workflow documentation for text file to excel format normalizer</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Interest Penalty Calculation - Variant 11 	 Id: TC0699 	 Description: Verify system handles invalid or missing data during Interest Penalty Calculation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Interest Penalty Calculation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Overview</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 11 	 Id: TC0678 	 Description: Verify claims rules engine properly calculates Provider NPI Verification 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for Provider NPI Verification 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>This document provides a comprehensive user guide for the Text File to Excel Conversion Workflow. The workflow is designed to automate the extraction</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> transformation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> and conversion of structured or semi-structured text file data into Microsoft Excel format.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Location Map View - Variant 4 	 Id: TC0242 	 Description: Verify behavior of Location Map View under standard network load conditions 	 Precondition: Database populated with active patient appointment records. 	 Test Step: 1 	 Test Step Description: Select the target option from 'My Appointments' view for Location Map View 	 Test Step Expected Result: Correct data visual tags render cleanly without page overflow.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2. Workflow Details</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Alert Dismissal Persistence - Variant 12 	 Id: TC0736 	 Description: Verify accuracy and SLA metrics for Alert Dismissal Persistence predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Alert Dismissal Persistence 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Workflow Name: Text to Excel Conversion</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Cost Spike Detection - Variant 19 	 Id: TC1129 	 Description: Verify AI pipeline capabilities when processing Cost Spike Detection 	 Precondition: AI predictive inference service active. 	 Test Step: 1 	 Test Step Description: Inject sample telemetry dataset into stream to evaluate Cost Spike Detection 	 Test Step Expected Result: AI processing layer identifies pattern and updates UI cards within SLA.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Workflow Purpose: Convert input text files into formatted Excel spreadsheets</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Maximum Out-of-Pocket Cap - Variant 22 	 Id: TC1344 	 Description: Verify system flags exception when Maximum Out-of-Pocket Cap criteria are met 	 Precondition: Fee schedule table configured in runtime memory. 	 Test Step: 1 	 Test Step Description: Inspect adjudication output parameters for Maximum Out-of-Pocket Cap 	 Test Step Expected Result: Financial liability split correctly between member and plan.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Workflow Type: Automated Data Transformation Workflow</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Automated Summary Generation - Variant 4 	 Id: TC0277 	 Description: Verify AI pipeline capabilities when processing Automated Summary Generation 	 Precondition: AI predictive inference service active. 	 Test Step: 1 	 Test Step Description: Inject sample telemetry dataset into stream to evaluate Automated Summary Generation 	 Test Step Expected Result: AI processing layer identifies pattern and updates UI cards within SLA.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Supported File Formats: .txt (customizable)</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 8 	 Id: TC0498 	 Description: Verify claims rules engine properly calculates Provider NPI Verification 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for Provider NPI Verification 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Output Format: Microsoft Excel (xlsx) (downloadable)</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Predictive No-Show Score - Variant 7 	 Id: TC0406 	 Description: Verify dashboard UI component displays output from Predictive No-Show Score 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Predictive No-Show Score 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Execution Mode: Manual</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Telehealth Link Generation - Variant 9 	 Id: TC0545 	 Description: Verify that Telehealth Link Generation operates correctly when loaded by patient user 	 Precondition: Patient user logged in with valid session token. 	 Test Step: 1 	 Test Step Description: Navigate to the Patient Portal dashboard and trigger Telehealth Link Generation 	 Test Step Expected Result: System successfully processes request and updates UI state within 2 seconds.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Expected Output: Structured Excel workbook with mapped columns and formatted data</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 19 	 Id: TC1162 	 Description: Verify dashboard UI component displays output from Historical Baseline Comparison 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Historical Baseline Comparison 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Workflow ID</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Reschedule Request - Variant 16 	 Id: TC0956 	 Description: Verify edge case data handling during Reschedule Request execution 	 Precondition: User profile settings configured with default preferences. 	 Test Step: 1 	 Test Step Description: Submit the request form and observe screen update for Reschedule Request 	 Test Step Expected Result: System logs action correctly and maintains complete session data integrity.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Workflow Name</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 18 	 Id: TC1102 	 Description: Verify dashboard UI component displays output from Historical Baseline Comparison 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Historical Baseline Comparison 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Workflow Actions</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Anomaly Detection Alert 	 Id: TC002 	 Description: Verify alert generation SLA when a product metric deviates from historical distribution boundaries 	 Precondition: Pre-trained predictive model cores are fully operational. 	 Test Step: 1 	 Test Step Description: Inject anomalous sample data stream into active processing queue paths. 	 Test Step Expected Result: AI processing layer intercepts structural boundary exception and sends a system alert UI notification within 2 seconds.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Input</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Adjustment Code Processing - Variant 21 	 Id: TC1275 	 Description: Verify system handles invalid or missing data during Adjustment Code Processing 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Adjustment Code Processing 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Output</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Alert Dismissal Persistence - Variant 8 	 Id: TC0496 	 Description: Verify accuracy and SLA metrics for Alert Dismissal Persistence predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Alert Dismissal Persistence 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">	17104</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Reschedule Request - Variant 12 	 Id: TC0716 	 Description: Verify edge case data handling during Reschedule Request execution 	 Precondition: User profile settings configured with default preferences. 	 Test Step: 1 	 Test Step Description: Submit the request form and observe screen update for Reschedule Request 	 Test Step Expected Result: System logs action correctly and maintains complete session data integrity.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Text to Excel Conversion 2</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 23 	 Id: TC1387 	 Description: Verify real-time notification trigger during False Positive Feedback Loop 	 Precondition: Kafka event streaming topic connected. 	 Test Step: 1 	 Test Step Description: Simulate statistical deviation vector to validate False Positive Feedback Loop 	 Test Step Expected Result: System generates high-priority notification banner instantly.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Convert input text files into formatted Excel spreadsheets</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Location Map View - Variant 21 	 Id: TC1262 	 Description: Verify behavior of Location Map View under standard network load conditions 	 Precondition: Database populated with active patient appointment records. 	 Test Step: 1 	 Test Step Description: Select the target option from 'My Appointments' view for Location Map View 	 Test Step Expected Result: Correct data visual tags render cleanly without page overflow.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Text File</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: EOB Document Generation - Variant 22 	 Id: TC1311 	 Description: Verify system handles invalid or missing data during EOB Document Generation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for EOB Document Generation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">	.xlsx document</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 4 	 Id: TC0234 	 Description: Verify claims rules engine properly calculates Claim Line Item Split 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for Claim Line Item Split 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3. Agent Details</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Location Map View - Variant 23 	 Id: TC1382 	 Description: Verify behavior of Location Map View under standard network load conditions 	 Precondition: Database populated with active patient appointment records. 	 Test Step: 1 	 Test Step Description: Select the target option from 'My Appointments' view for Location Map View 	 Test Step Expected Result: Correct data visual tags render cleanly without page overflow.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Agent Name: Text To Excel Transformation Agent</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 23 	 Id: TC1398 	 Description: Verify claims rules engine properly calculates Provider NPI Verification 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for Provider NPI Verification 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agent Description: This agent restructures unstructured or semi-structured text into clean Excel spreadsheets and provides users with a direct download link. </t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Bundled Service Deduction - Variant 22 	 Id: TC1341 	 Description: Verify adjudication engine logic for Bundled Service Deduction 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Bundled Service Deduction into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execution Permissions: Read/Write access to source and destination folders in GitHub.</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Print Summary - Variant 23 	 Id: TC1394 	 Description: Verify behavior of Print Summary under standard network load conditions 	 Precondition: Database populated with active patient appointment records. 	 Test Step: 1 	 Test Step Description: Select the target option from 'My Appointments' view for Print Summary 	 Test Step Expected Result: Correct data visual tags render cleanly without page overflow.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Monitoring Capability: Workflow execution logs and alert notifications</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Explanation Tooltip Generation - Variant 3 	 Id: TC0193 	 Description: Verify AI pipeline capabilities when processing Explanation Tooltip Generation 	 Precondition: AI predictive inference service active. 	 Test Step: 1 	 Test Step Description: Inject sample telemetry dataset into stream to evaluate Explanation Tooltip Generation 	 Test Step Expected Result: AI processing layer identifies pattern and updates UI cards within SLA.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Agent Name</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Predictive No-Show Score - Variant 10 	 Id: TC0586 	 Description: Verify dashboard UI component displays output from Predictive No-Show Score 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Predictive No-Show Score 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Mapped Workflow ID</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Maximum Out-of-Pocket Cap - Variant 8 	 Id: TC0504 	 Description: Verify system flags exception when Maximum Out-of-Pocket Cap criteria are met 	 Precondition: Fee schedule table configured in runtime memory. 	 Test Step: 1 	 Test Step Description: Inspect adjudication output parameters for Maximum Out-of-Pocket Cap 	 Test Step Expected Result: Financial liability split correctly between member and plan.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Actions</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Mobile Responsive Grid - Variant 10 	 Id: TC0635 	 Description: Verify UI validation and error handling for Mobile Responsive Grid 	 Precondition: Mock scheduling API server online and reachable. 	 Test Step: 1 	 Test Step Description: Execute user interaction sequence corresponding to Mobile Responsive Grid 	 Test Step Expected Result: Appropriate status indicator displays with expected confirmation message.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Outputs</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Confidence Threshold Filter - Variant 3 	 Id: TC0184 	 Description: Verify accuracy and SLA metrics for Confidence Threshold Filter predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Confidence Threshold Filter 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Tools Used</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Timezone Sync - Variant 6 	 Id: TC0341 	 Description: Verify that Timezone Sync operates correctly when loaded by patient user 	 Precondition: Patient user logged in with valid session token. 	 Test Step: 1 	 Test Step Description: Navigate to the Patient Portal dashboard and trigger Timezone Sync 	 Test Step Expected Result: System successfully processes request and updates UI state within 2 seconds.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Knowledge Base</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: High Value Claim Audit Trigger - Variant 3 	 Id: TC0210 	 Description: Verify claims rules engine properly calculates High Value Claim Audit Trigger 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for High Value Claim Audit Trigger 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Text To Excel Transformation Agent</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Timely Filing Limit Edge - Variant 7 	 Id: TC0426 	 Description: Verify claims rules engine properly calculates Timely Filing Limit Edge 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for Timely Filing Limit Edge 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">	17104</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Reschedule Request - Variant 8 	 Id: TC0476 	 Description: Verify edge case data handling during Reschedule Request execution 	 Precondition: User profile settings configured with default preferences. 	 Test Step: 1 	 Test Step Description: Submit the request form and observe screen update for Reschedule Request 	 Test Step Expected Result: System logs action correctly and maintains complete session data integrity.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">	· File extraction and conversion</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: Check-in Status Indicator - Variant 20 	 Id: TC1226 	 Description: Verify behavior of Check-in Status Indicator under standard network load conditions 	 Precondition: Database populated with active patient appointment records. 	 Test Step: 1 	 Test Step Description: Select the target option from 'My Appointments' view for Check-in Status Indicator 	 Test Step Expected Result: Correct data visual tags render cleanly without page overflow.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">	.xlsx document</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: EOB Document Generation - Variant 9 	 Id: TC0531 	 Description: Verify system handles invalid or missing data during EOB Document Generation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for EOB Document Generation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Text-to-Excel Generator</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Timely Filing Limit Edge - Variant 20 	 Id: TC1206 	 Description: Verify claims rules engine properly calculates Timely Filing Limit Edge 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for Timely Filing Limit Edge 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">	NA</t>
+          <t xml:space="preserve">	Work Item ID: 1571 	 Module: Patient Portal Appointments 	 Name: No Appointments Empty State - Variant 20 	 Id: TC1229 	 Description: Verify that No Appointments Empty State operates correctly when loaded by patient user 	 Precondition: Patient user logged in with valid session token. 	 Test Step: 1 	 Test Step Description: Navigate to the Patient Portal dashboard and trigger No Appointments Empty State 	 Test Step Expected Result: System successfully processes request and updates UI state within 2 seconds.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4. Tool Details</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 17 	 Id: TC1042 	 Description: Verify dashboard UI component displays output from Historical Baseline Comparison 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Historical Baseline Comparison 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tool Name: Text-to-Excel Generator</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Timely Filing Limit Edge - Variant 9 	 Id: TC0546 	 Description: Verify claims rules engine properly calculates Timely Filing Limit Edge 	 Precondition: Member eligibility database active and updated. 	 Test Step: 1 	 Test Step Description: Trigger automated rules evaluation pipeline for Timely Filing Limit Edge 	 Test Step Expected Result: Claim status transitions to expected terminal state with proper reason code.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Primary Function: Converts raw text content into structured Excel spreadsheets dynamically.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Unusual Billing Pattern Flag - Variant 9 	 Id: TC0571 	 Description: Verify real-time notification trigger during Unusual Billing Pattern Flag 	 Precondition: Kafka event streaming topic connected. 	 Test Step: 1 	 Test Step Description: Simulate statistical deviation vector to validate Unusual Billing Pattern Flag 	 Test Step Expected Result: System generates high-priority notification banner instantly.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Core Processing Engine: Uses Pandas DataFrame Transformation and OpenPyXL Excel generation.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Procedure Code Cross-check - Variant 3 	 Id: TC1593 	 Description: Verify adjudication engine logic for Procedure Code Cross-check 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Procedure Code Cross-check into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dynamic Header Detection: Automatically identifies delimiters such as pipe (|) and comma (</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>).</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Interest Penalty Calculation - Variant 22 	 Id: TC2379 	 Description: Verify system handles invalid or missing data during Interest Penalty Calculation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Interest Penalty Calculation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JSON Parsing Capability: Supports valid and malformed JSON structure recovery using heuristic repair logic.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Bundled Service Deduction - Variant 10 	 Id: TC1887 	 Description: Verify system handles invalid or missing data during Bundled Service Deduction 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Bundled Service Deduction 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fallback Extraction Logic: Uses regex-based key-value extraction when standard JSON parsing fails.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Real-time Stream Ingestion - Variant 19 	 Id: TC2234 	 Description: Verify dashboard UI component displays output from Real-time Stream Ingestion 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Real-time Stream Ingestion 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Multi-line Record Handling: Merges broken or wrapped text lines into the correct data rows.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Corrected Claim Resubmission - Variant 9 	 Id: TC1857 	 Description: Verify adjudication engine logic for Corrected Claim Resubmission 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Corrected Claim Resubmission into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Schema Matrix Normalization: Dynamically aligns parent-child row structures into tabular format.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Procedure Code Cross-check - Variant 25 	 Id: TC2473 	 Description: Verify adjudication engine logic for Procedure Code Cross-check 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Procedure Code Cross-check into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GitHub Integration: Uploads generated Excel files directly into a specified GitHub repository using GitHub REST API.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Feature Attribution UI - Variant 14 	 Id: TC2032 	 Description: Verify accuracy and SLA metrics for Feature Attribution UI predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Feature Attribution UI 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Authentication Method: Uses GitHub Personal Access Token (PAT) for secure repository access.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 2 	 Id: TC1558 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Supported Output Format: Microsoft Excel (.xlsx).</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: SLA Performance Tracking - Variant 26 	 Id: TC2530 	 Description: Verify dashboard UI component displays output from SLA Performance Tracking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for SLA Performance Tracking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Error Handling: Detects empty content</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> invalid layouts</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> GitHub upload failures</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> and transformation exceptions.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Custom Threshold Setting - Variant 12 	 Id: TC1966 	 Description: Verify dashboard UI component displays output from Custom Threshold Setting 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Custom Threshold Setting 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Libraries Used: Pandas</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Requests</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OpenPyXL</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Pydantic</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Base64</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Regex (re)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> JSON.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Unusual Billing Pattern Flag - Variant 22 	 Id: TC2374 	 Description: Verify dashboard UI component displays output from Unusual Billing Pattern Flag 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Unusual Billing Pattern Flag 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Logging Utility: Captures execution logs and error details</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Corrected Claim Resubmission - Variant 1 	 Id: TC1537 	 Description: Verify adjudication engine logic for Corrected Claim Resubmission 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Corrected Claim Resubmission into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5. Input Parameters</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Batch Model Scoring - Variant 1 	 Id: TC1520 	 Description: Verify accuracy and SLA metrics for Batch Model Scoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Batch Model Scoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>The following parameters are required before executing the workflow:</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: High Value Claim Audit Trigger - Variant 11 	 Id: TC1933 	 Description: Verify adjudication engine logic for High Value Claim Audit Trigger 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing High Value Claim Audit Trigger into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Parameter</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Corrected Claim Resubmission - Variant 8 	 Id: TC1817 	 Description: Verify adjudication engine logic for Corrected Claim Resubmission 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Corrected Claim Resubmission into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Description</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: EOB Document Generation - Variant 26 	 Id: TC2507 	 Description: Verify system handles invalid or missing data during EOB Document Generation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for EOB Document Generation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Example</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Patient Risk Stratification - Variant 19 	 Id: TC2256 	 Description: Verify accuracy and SLA metrics for Patient Risk Stratification predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Patient Risk Stratification 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Input text file</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 29 	 Id: TC2630 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Text file input file to be uploaded</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Out-of-Network Coinsurance - Variant 8 	 Id: TC1783 	 Description: Verify system handles invalid or missing data during Out-of-Network Coinsurance 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Out-of-Network Coinsurance 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">	data.txt uploaded as workflow input</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 11 	 Id: TC1908 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">	GitHub token</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: EOB Document Generation - Variant 15 	 Id: TC2067 	 Description: Verify system handles invalid or missing data during EOB Document Generation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for EOB Document Generation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Access token for GitHub</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 15 	 Id: TC2068 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">	ghp_L3wDyRoieUYLZ49hPKt</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Batch Claim Ingestion - Variant 20 	 Id: TC2291 	 Description: Verify system handles invalid or missing data during Batch Claim Ingestion 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Batch Claim Ingestion 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">	GitHub Repo Owner</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Maximum Out-of-Pocket Cap - Variant 6 	 Id: TC1729 	 Description: Verify adjudication engine logic for Maximum Out-of-Pocket Cap 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Maximum Out-of-Pocket Cap into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Owner name for the GitHub repo</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Alert Dismissal Persistence - Variant 4 	 Id: TC1644 	 Description: Verify accuracy and SLA metrics for Alert Dismissal Persistence predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Alert Dismissal Persistence 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">	NavneetBN47</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Data Pipeline Health Monitor - Variant 4 	 Id: TC1652 	 Description: Verify accuracy and SLA metrics for Data Pipeline Health Monitor predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Data Pipeline Health Monitor 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">	GitHub Repo Name</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Batch Claim Ingestion - Variant 1 	 Id: TC1531 	 Description: Verify system handles invalid or missing data during Batch Claim Ingestion 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Batch Claim Ingestion 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Repository name</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Feature Attribution UI - Variant 25 	 Id: TC2472 	 Description: Verify accuracy and SLA metrics for Feature Attribution UI predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Feature Attribution UI 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">	testX</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Primary vs Secondary Payer - Variant 12 	 Id: TC1959 	 Description: Verify system handles invalid or missing data during Primary vs Secondary Payer 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Primary vs Secondary Payer 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Output file Name</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 23 	 Id: TC2389 	 Description: Verify adjudication engine logic for Claim Line Item Split 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Claim Line Item Split into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Required name for the downloadable excel file</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: EOB Document Generation - Variant 27 	 Id: TC2547 	 Description: Verify system handles invalid or missing data during EOB Document Generation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for EOB Document Generation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Testcases (no suffix required)</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 14 	 Id: TC2028 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6. Prerequisites</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Retraining Trigger - Variant 16 	 Id: TC2140 	 Description: Verify accuracy and SLA metrics for Model Retraining Trigger predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Retraining Trigger 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">AAVA int 2.0 access </t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Unusual Billing Pattern Flag - Variant 18 	 Id: TC2214 	 Description: Verify dashboard UI component displays output from Unusual Billing Pattern Flag 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Unusual Billing Pattern Flag 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Access to Quality Engineering realm.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Predictive No-Show Score - Variant 11 	 Id: TC1904 	 Description: Verify accuracy and SLA metrics for Predictive No-Show Score predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Predictive No-Show Score 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GitHub repository setup.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Alert Dismissal Persistence - Variant 6 	 Id: TC1724 	 Description: Verify accuracy and SLA metrics for Alert Dismissal Persistence predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Alert Dismissal Persistence 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>User must have access permissions to input/output directories.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Corrected Claim Resubmission - Variant 21 	 Id: TC2337 	 Description: Verify adjudication engine logic for Corrected Claim Resubmission 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Corrected Claim Resubmission into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Microsoft Excel or compatible spreadsheet software should be available for validation.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Interest Penalty Calculation - Variant 17 	 Id: TC2179 	 Description: Verify system handles invalid or missing data during Interest Penalty Calculation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Interest Penalty Calculation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7. Execution Steps</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Cost Spike Detection - Variant 10 	 Id: TC1866 	 Description: Verify dashboard UI component displays output from Cost Spike Detection 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Cost Spike Detection 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Place the source text file in the configured input directory of the workflow.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Diagnosis Code Validation - Variant 25 	 Id: TC2471 	 Description: Verify system handles invalid or missing data during Diagnosis Code Validation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Diagnosis Code Validation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Provide required input parameters and execute.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Patient Risk Stratification - Variant 10 	 Id: TC1896 	 Description: Verify accuracy and SLA metrics for Patient Risk Stratification predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Patient Risk Stratification 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Monitor execution logs for successful completion.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Interest Penalty Calculation - Variant 23 	 Id: TC2419 	 Description: Verify system handles invalid or missing data during Interest Penalty Calculation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Interest Penalty Calculation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Verify generated Excel output by downloading from the URL provided in the workflow output.</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Custom Threshold Setting - Variant 21 	 Id: TC2326 	 Description: Verify dashboard UI component displays output from Custom Threshold Setting 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Custom Threshold Setting 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8. Error Handling &amp; Troubleshooting</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Tax ID Validation - Variant 7 	 Id: TC1775 	 Description: Verify system handles invalid or missing data during Tax ID Validation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Tax ID Validation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Invalid file format – Ensure the source file is supported</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Confidence Threshold Filter - Variant 23 	 Id: TC2396 	 Description: Verify accuracy and SLA metrics for Confidence Threshold Filter predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Confidence Threshold Filter 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Permission denied – Verify folder access permissions.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Maximum Out-of-Pocket Cap - Variant 7 	 Id: TC1769 	 Description: Verify adjudication engine logic for Maximum Out-of-Pocket Cap 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Maximum Out-of-Pocket Cap into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Empty output file – Validate source file contents.</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Duplicate Claim Rejection - Variant 11 	 Id: TC1915 	 Description: Verify system handles invalid or missing data during Duplicate Claim Rejection 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Duplicate Claim Rejection 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Workflow failure – Review execution logs for detailed error messages</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 22 	 Id: TC2358 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Common failure RCA – Ensure tool attachment in agent</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> verify repository access and token expiry.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 10 	 Id: TC1885 	 Description: Verify adjudication engine logic for Provider NPI Verification 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Provider NPI Verification into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9. Example Execution Details</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Corrected Claim Resubmission - Variant 25 	 Id: TC2497 	 Description: Verify adjudication engine logic for Corrected Claim Resubmission 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Corrected Claim Resubmission into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Execution ID : 740e7f859-3ff9-464a-aded-8c25e077c353</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 24 	 Id: TC2448 	 Description: Verify accuracy and SLA metrics for Historical Baseline Comparison predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Historical Baseline Comparison 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Execution logs : AAVA Launchpad – AI Agent Platform by Ascendion</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Pre-authorization Check - Variant 27 	 Id: TC2545 	 Description: Verify adjudication engine logic for Pre-authorization Check 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Pre-authorization Check into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Input file : </t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Adjustment Code Processing - Variant 6 	 Id: TC1723 	 Description: Verify system handles invalid or missing data during Adjustment Code Processing 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Adjustment Code Processing 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Output file : </t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 15 	 Id: TC2085 	 Description: Verify adjudication engine logic for Provider NPI Verification 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Provider NPI Verification into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>testcases delimited.txt</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Primary vs Secondary Payer - Variant 17 	 Id: TC2159 	 Description: Verify system handles invalid or missing data during Primary vs Secondary Payer 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Primary vs Secondary Payer 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Scenario ID|Scenario Title|Test Case ID|Test Case Title|Preconditions|Test Type|Automation Feasible|Test Data|Step #|Test Step Description|Expected Result</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 13 	 Id: TC2008 	 Description: Verify accuracy and SLA metrics for Historical Baseline Comparison predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Historical Baseline Comparison 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TC001|US32275|Plan Recommendation|Verify side-by-side plan comparison|User is logged into the CareSource enrollment portal and has completed the health needs questionnaire|Functional|Yes|User with completed profile and at least two recommended plans|1|Navigate to plan recommendation page|System displays side-by-side comparison of at least two plans highlighting premiums</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> deductibles</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> co-pays</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> out-of-pocket maximums</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> and coverage for specified medications and doctors</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: SLA Performance Tracking - Variant 1 	 Id: TC1530 	 Description: Verify dashboard UI component displays output from SLA Performance Tracking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for SLA Performance Tracking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>||||||||2|Review plan features and select a plan|Selected plan is highlighted and user can proceed to enrollment</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Adjustment Code Processing - Variant 25 	 Id: TC2483 	 Description: Verify system handles invalid or missing data during Adjustment Code Processing 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Adjustment Code Processing 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TC002|US32275|Plan Recommendation|Verify navigation to enrollment after plan selection|User is on the plan comparison page|Functional|Yes|User with at least one recommended plan|1|Select a plan and click 'Enroll'|System transitions to the enrollment process with the chosen plan pre-selected</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 10 	 Id: TC1878 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TC003|US32275|Plan Recommendation|Negative - No recommended plans|User has completed health needs but no plans match criteria|Negative|Yes|User with uncommon criteria resulting in no matches|1|Navigate to plan recommendation page|System displays a message: "No plans match your criteria. Please adjust your preferences."</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 12 	 Id: TC1958 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TC004|US32275|Plan Recommendation|Edge - Maximum number of plans|User qualifies for 10+ plans|Edge|Yes|User with broad criteria resulting in maximum recommendations|1|Navigate to plan recommendation page|System displays all recommended plans in a scrollable</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> readable format without UI breakage</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Automated Summary Generation - Variant 5 	 Id: TC1698 	 Description: Verify dashboard UI component displays output from Automated Summary Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Automated Summary Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TC005|US32274|Plan Personalization|Verify member can input medications and providers|User is authenticated|Functional|Yes|Medication: Metformin 500mg</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Provider: Dr. Smith|1|Navigate to health needs input page|System displays input fields for medications and providers</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Interest Penalty Calculation - Variant 13 	 Id: TC2019 	 Description: Verify system handles invalid or missing data during Interest Penalty Calculation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Interest Penalty Calculation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>||||||||2|Enter medication and provider information and submit|System accepts input</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> validates data</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> and confirms successful entry</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Adjustment Code Processing - Variant 15 	 Id: TC2083 	 Description: Verify system handles invalid or missing data during Adjustment Code Processing 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Adjustment Code Processing 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TC006|US32274|Plan Personalization|Verify financial preference input|User is authenticated|Functional|Yes|Premium: $200</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Deductible: $1000</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OOP Max: $5000|1|Navigate to financial preferences section|System displays fields for premium</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> deductible</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> and out-of-pocket maximum</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Pre-authorization Check - Variant 21 	 Id: TC2305 	 Description: Verify adjudication engine logic for Pre-authorization Check 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Pre-authorization Check into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>||||||||2|Enter preferences and submit|System saves preferences and updates recommendation criteria</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Data Pipeline Health Monitor - Variant 6 	 Id: TC1732 	 Description: Verify accuracy and SLA metrics for Data Pipeline Health Monitor predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Data Pipeline Health Monitor 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TC007|US32274|Plan Personalization|Negative - Invalid medication entry|User is authenticated|Negative|Yes|Medication: "" (blank entry)|1|Leave medication field blank and submit|System displays error: "Medication name required"</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Tax ID Validation - Variant 1 	 Id: TC1535 	 Description: Verify system handles invalid or missing data during Tax ID Validation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Tax ID Validation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TC008|US32274|Plan Personalization|Edge - Large medication list|User is authenticated|Edge|Yes|Medication: 20+ entries|1|Enter 20+ medications and submit|System accepts all entries and processes recommendations without error</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: SLA Performance Tracking - Variant 5 	 Id: TC1690 	 Description: Verify dashboard UI component displays output from SLA Performance Tracking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for SLA Performance Tracking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TC009|US32273|Guided Enrollment|Verify guided workflow for plan selection|User is a prospective member|Functional|Yes|Health: Asthma</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PCP: Dr. Lee</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Premium: $150|1|Start guided enrollment|System prompts for health data</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> provider</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> and financial preferences in sequence</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 19 	 Id: TC2229 	 Description: Verify adjudication engine logic for Claim Line Item Split 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Claim Line Item Split into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>||||||||2|Complete all steps and submit|System generates and displays personalized plan recommendations with comparison tool</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Patient Risk Stratification - Variant 18 	 Id: TC2216 	 Description: Verify accuracy and SLA metrics for Patient Risk Stratification predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Patient Risk Stratification 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TC010|US32273|Guided Enrollment|Negative - Missing required fields|User is a prospective member|Negative|Yes|Omit required health data|1|Attempt to proceed without entering all required fields|System displays validation errors for missing fields</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 25 	 Id: TC2470 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TC011|US32273|Guided Enrollment|Edge - Extreme cost preferences|User is a prospective member|Edge|Yes|Premium: $0</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Deductible: $0|1|Enter extreme values and submit|System processes and displays only plans meeting criteria</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> or a message if none available</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Interest Penalty Calculation - Variant 18 	 Id: TC2219 	 Description: Verify system handles invalid or missing data during Interest Penalty Calculation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Interest Penalty Calculation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TC012|US31822|Demographic Input|Verify demographic and health needs input|User is a prospective member|Functional|Yes|Age: 40</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Location: OH</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Doctor: Dr. Adams</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Medication: Lisinopril|1|Navigate to demographic input page|System displays fields for age</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> location</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> doctors</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> medications</t>
-        </is>
-      </c>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Cost Spike Detection - Variant 26 	 Id: TC2506 	 Description: Verify dashboard UI component displays output from Cost Spike Detection 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Cost Spike Detection 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>||||||||2|Enter data and submit|System validates and accepts input</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> proceeding to recommendations</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Cost Spike Detection - Variant 17 	 Id: TC2146 	 Description: Verify dashboard UI component displays output from Cost Spike Detection 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Cost Spike Detection 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TC013|US31822|Demographic Input|Negative - Invalid age|User is a prospective member|Negative|Yes|Age: -1|1|Enter invalid age and submit|System displays error: "Invalid age"</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 14 	 Id: TC2038 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TC014|US31822|Demographic Input|Edge - Maximum field length|User is a prospective member|Edge|Yes|Doctor name: 100+ characters|1|Enter maximum length for doctor name and submit|System accepts or displays appropriate error without crashing</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 28 	 Id: TC2598 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TC015|US32306|Profile|Verify profile view|User is logged in|Functional|Yes|User with profile data|1|Navigate to profile page|System displays correct profile information</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Explanation Tooltip Generation - Variant 21 	 Id: TC2322 	 Description: Verify dashboard UI component displays output from Explanation Tooltip Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Explanation Tooltip Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TC016|US32307|Settings|Verify settings update|User is logged in|Functional|Yes|New notification preference|1|Go to settings</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> change preference</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> save|System updates and confirms setting change</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Denial Code ERR-ENR-02 - Variant 22 	 Id: TC2361 	 Description: Verify adjudication engine logic for Denial Code ERR-ENR-02 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Denial Code ERR-ENR-02 into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TC017|US32308|Transaction History|Verify transaction history view|User is logged in|Functional|Yes|User with transaction history|1|Navigate to transaction history|System displays all past transactions</t>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 17 	 Id: TC2148 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TC018|US32309|Search and Filter|Verify data search and filter|User is logged in|Functional|Yes|Search: "Diabetes"</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Filter: Date range|1|Enter search term and filter|System returns correct filtered data</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: SLA Performance Tracking - Variant 11 	 Id: TC1930 	 Description: Verify dashboard UI component displays output from SLA Performance Tracking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for SLA Performance Tracking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TC019|US32310|Export Reports|Verify report export|User is logged in|Functional|Yes|Report: Claims|1|Click export on claims report|System downloads report in selected format</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Timely Filing Limit Edge - Variant 3 	 Id: TC1597 	 Description: Verify adjudication engine logic for Timely Filing Limit Edge 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Timely Filing Limit Edge into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TC020|US32311|User Permissions|Verify permission management|Admin user logged in|Functional|Yes|Assign 'Editor' to user X|1|Navigate to permissions</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> assign role|System saves and reflects new permission</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Explanation Tooltip Generation - Variant 16 	 Id: TC2122 	 Description: Verify dashboard UI component displays output from Explanation Tooltip Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Explanation Tooltip Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TC021|US32312|System Logs|Verify system log view|Admin user logged in|Functional|Yes|Any log record|1|Navigate to system logs|System displays logs with timestamp</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> user</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> action</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Tax ID Validation - Variant 28 	 Id: TC2615 	 Description: Verify system handles invalid or missing data during Tax ID Validation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Tax ID Validation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TC022|US32304|Password Reset|Verify password reset|User on login page|Functional|Yes|Registered email|1|Click 'Forgot Password'</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> enter email|System sends reset link to email</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 29 	 Id: TC2629 	 Description: Verify adjudication engine logic for Claim Line Item Split 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Claim Line Item Split into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TC023|US32305|Two-Factor Authentication|Verify 2FA enablement|User is logged in|Functional|Yes|Valid phone number|1|Navigate to security</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> enable 2FA|System sends code and confirms setup</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Custom Threshold Setting - Variant 5 	 Id: TC1686 	 Description: Verify dashboard UI component displays output from Custom Threshold Setting 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Custom Threshold Setting 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TC024|US32303|Login|Verify email login|User is registered|Functional|Yes|Valid email/password|1|Enter credentials</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> click login|System authenticates and redirects to dashboard</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Batch Claim Ingestion - Variant 29 	 Id: TC2651 	 Description: Verify system handles invalid or missing data during Batch Claim Ingestion 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Batch Claim Ingestion 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TC025|US32983|NEW STORY TETS|Basic smoke test|System available|Functional|Yes|N/A|1|Access feature|Feature loads without error</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Negative - API Gateway Timeout 	 Id: TC038 	 Description: Verify system message presentation layers when database connections time out 	 Precondition: Telemetry services unavailable. 	 Test Step: 1 	 Test Step Description: Force an artificial data refresh sequence during downstream infrastructure downtime. 	 Test Step Expected Result: Dashboard handles timeout exception gracefully</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> rendering an alert mask: 'Analytics Data Synchronizer unavailable. Please retry later.'</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TC026|US32744|member 1|Basic smoke test|System available|Functional|Yes|N/A|1|Access feature|Feature loads without error</t>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: EOB Document Generation - Variant 4 	 Id: TC1627 	 Description: Verify system handles invalid or missing data during EOB Document Generation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for EOB Document Generation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Custom Threshold Setting - Variant 4 	 Id: TC1646 	 Description: Verify dashboard UI component displays output from Custom Threshold Setting 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Custom Threshold Setting 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Predictive No-Show Score - Variant 16 	 Id: TC2104 	 Description: Verify accuracy and SLA metrics for Predictive No-Show Score predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Predictive No-Show Score 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 12 	 Id: TC1948 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Bundled Service Deduction - Variant 28 	 Id: TC2607 	 Description: Verify system handles invalid or missing data during Bundled Service Deduction 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Bundled Service Deduction 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 24 	 Id: TC2429 	 Description: Verify adjudication engine logic for Claim Line Item Split 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Claim Line Item Split into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Primary vs Secondary Payer - Variant 20 	 Id: TC2279 	 Description: Verify system handles invalid or missing data during Primary vs Secondary Payer 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Primary vs Secondary Payer 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: SLA Performance Tracking - Variant 25 	 Id: TC2490 	 Description: Verify dashboard UI component displays output from SLA Performance Tracking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for SLA Performance Tracking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: In-Network Co-pay Calculation - Variant 27 	 Id: TC2541 	 Description: Verify adjudication engine logic for In-Network Co-pay Calculation 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing In-Network Co-pay Calculation into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 3 	 Id: TC1605 	 Description: Verify adjudication engine logic for Provider NPI Verification 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Provider NPI Verification into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Confidence Threshold Filter - Variant 25 	 Id: TC2476 	 Description: Verify accuracy and SLA metrics for Confidence Threshold Filter predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Confidence Threshold Filter 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Alert Dismissal Persistence - Variant 19 	 Id: TC2244 	 Description: Verify accuracy and SLA metrics for Alert Dismissal Persistence predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Alert Dismissal Persistence 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Explainability UI Popover 	 Id: TC011 	 Description: Verify clear and understandable natural language explanation rendering for AI insights 	 Precondition: AI generated insights are visible on screen. 	 Test Step: 1 	 Test Step Description: Click 'Request Explanation' hyperlink on an active trend item card. 	 Test Step Expected Result: System renders a popup window containing mathematical contribution factors in clear</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> plain text format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Security - Data Leak Check 	 Id: TC026 	 Description: Verify strict data privacy enforcement limits during ML telemetry generation passes 	 Precondition: Multi-tenant data partitioning configured. 	 Test Step: 1 	 Test Step Description: Execute batch analysis requests concurrently across tenant boundaries. 	 Test Step Expected Result: Internal data isolation perimeter blocks crossover references; generated insights strictly contain isolated single-tenant telemetry scopes.</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Confidence Threshold Filter - Variant 29 	 Id: TC2636 	 Description: Verify accuracy and SLA metrics for Confidence Threshold Filter predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Confidence Threshold Filter 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Trend Anomaly Alert - Variant 16 	 Id: TC2102 	 Description: Verify dashboard UI component displays output from Trend Anomaly Alert 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Trend Anomaly Alert 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Predictive No-Show Score - Variant 28 	 Id: TC2584 	 Description: Verify accuracy and SLA metrics for Predictive No-Show Score predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Predictive No-Show Score 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Automated Summary Generation - Variant 7 	 Id: TC1778 	 Description: Verify dashboard UI component displays output from Automated Summary Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Automated Summary Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Timely Filing Limit Edge - Variant 10 	 Id: TC1877 	 Description: Verify adjudication engine logic for Timely Filing Limit Edge 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Timely Filing Limit Edge into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Real-time Stream Ingestion - Variant 8 	 Id: TC1794 	 Description: Verify dashboard UI component displays output from Real-time Stream Ingestion 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Real-time Stream Ingestion 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Automated Summary Generation - Variant 16 	 Id: TC2138 	 Description: Verify dashboard UI component displays output from Automated Summary Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Automated Summary Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Trend Anomaly Alert - Variant 6 	 Id: TC1702 	 Description: Verify dashboard UI component displays output from Trend Anomaly Alert 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Trend Anomaly Alert 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Maximum Out-of-Pocket Cap - Variant 4 	 Id: TC1649 	 Description: Verify adjudication engine logic for Maximum Out-of-Pocket Cap 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Maximum Out-of-Pocket Cap into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Real-time Stream Ingestion - Variant 12 	 Id: TC1954 	 Description: Verify dashboard UI component displays output from Real-time Stream Ingestion 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Real-time Stream Ingestion 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Alert Dismissal Persistence - Variant 2 	 Id: TC1564 	 Description: Verify accuracy and SLA metrics for Alert Dismissal Persistence predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Alert Dismissal Persistence 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Duplicate Detection Flow 	 Id: TC024 	 Description: Verify systemic blocking of duplicate out-of-network claims 	 Precondition: Identical claim processed 5 minutes prior. 	 Test Step: 1 	 Test Step Description: Submit an identical out-of-network claim for the same diagnostic service date. 	 Test Step Expected Result: System intercepts row and flags status as 'Rejected-Duplicate' using reference block code 'ERR-DUP-04'.</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Batch Model Scoring - Variant 22 	 Id: TC2360 	 Description: Verify accuracy and SLA metrics for Batch Model Scoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Batch Model Scoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: High Value Claim Audit Trigger - Variant 26 	 Id: TC2533 	 Description: Verify adjudication engine logic for High Value Claim Audit Trigger 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing High Value Claim Audit Trigger into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Trend Anomaly Alert - Variant 20 	 Id: TC2262 	 Description: Verify dashboard UI component displays output from Trend Anomaly Alert 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Trend Anomaly Alert 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Retraining Trigger - Variant 7 	 Id: TC1780 	 Description: Verify accuracy and SLA metrics for Model Retraining Trigger predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Retraining Trigger 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 25 	 Id: TC2468 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Out-of-Network Coinsurance - Variant 7 	 Id: TC1743 	 Description: Verify system handles invalid or missing data during Out-of-Network Coinsurance 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Out-of-Network Coinsurance 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Tax ID Validation - Variant 27 	 Id: TC2575 	 Description: Verify system handles invalid or missing data during Tax ID Validation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Tax ID Validation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Real-time Stream Ingestion - Variant 18 	 Id: TC2194 	 Description: Verify dashboard UI component displays output from Real-time Stream Ingestion 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Real-time Stream Ingestion 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Confidence Threshold Filter - Variant 28 	 Id: TC2596 	 Description: Verify accuracy and SLA metrics for Confidence Threshold Filter predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Confidence Threshold Filter 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Explanation Tooltip Generation - Variant 22 	 Id: TC2362 	 Description: Verify dashboard UI component displays output from Explanation Tooltip Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Explanation Tooltip Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Pre-authorization Check - Variant 18 	 Id: TC2185 	 Description: Verify adjudication engine logic for Pre-authorization Check 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Pre-authorization Check into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Feature Attribution UI - Variant 12 	 Id: TC1952 	 Description: Verify accuracy and SLA metrics for Feature Attribution UI predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Feature Attribution UI 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Deductible Not Met Flow - EDI 	 Id: TC027 	 Description: Verify EDI 277 generation status update occurs automatically 	 Precondition: Member is enrolled. OON deductible balance is $1000. 	 Test Step: 1 	 Test Step Description: Check outbound communication logs for transaction confirmation. 	 Test Step Expected Result: System automatically triggers and transmits an EDI 277 status update detailing the pending status within SLA bounds.</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Automated Summary Generation - Variant 15 	 Id: TC2098 	 Description: Verify dashboard UI component displays output from Automated Summary Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Automated Summary Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Trend Anomaly Alert - Variant 4 	 Id: TC1622 	 Description: Verify dashboard UI component displays output from Trend Anomaly Alert 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Trend Anomaly Alert 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Batch Model Scoring - Variant 20 	 Id: TC2280 	 Description: Verify accuracy and SLA metrics for Batch Model Scoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Batch Model Scoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Feature Attribution UI - Variant 13 	 Id: TC1992 	 Description: Verify accuracy and SLA metrics for Feature Attribution UI predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Feature Attribution UI 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 3 	 Id: TC1608 	 Description: Verify accuracy and SLA metrics for Historical Baseline Comparison predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Historical Baseline Comparison 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 22 	 Id: TC2350 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Primary vs Secondary Payer - Variant 2 	 Id: TC1559 	 Description: Verify system handles invalid or missing data during Primary vs Secondary Payer 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Primary vs Secondary Payer 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Real-time Stream Ingestion - Variant 11 	 Id: TC1914 	 Description: Verify dashboard UI component displays output from Real-time Stream Ingestion 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Real-time Stream Ingestion 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Unusual Billing Pattern Flag - Variant 7 	 Id: TC1774 	 Description: Verify dashboard UI component displays output from Unusual Billing Pattern Flag 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Unusual Billing Pattern Flag 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: In-Network Co-pay Calculation - Variant 12 	 Id: TC1941 	 Description: Verify adjudication engine logic for In-Network Co-pay Calculation 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing In-Network Co-pay Calculation into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: In-Network Co-pay Calculation - Variant 16 	 Id: TC2101 	 Description: Verify adjudication engine logic for In-Network Co-pay Calculation 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing In-Network Co-pay Calculation into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Edge - Borderline Deviation Limit 	 Id: TC008 	 Description: Verify anomaly classification threshold criteria right at model mathematical limits 	 Precondition: Model boundary trigger point set precisely to 3.0 standard deviations. 	 Test Step: 1 	 Test Step Description: Transmit precise edge metric adjustment dataset row items. 	 Test Step Expected Result: System correctly isolates border fluctuation as an active deviation anomaly</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> outputting accurate diagnostic reporting values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 24 	 Id: TC2445 	 Description: Verify adjudication engine logic for Provider NPI Verification 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Provider NPI Verification into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Custom Threshold Setting - Variant 7 	 Id: TC1766 	 Description: Verify dashboard UI component displays output from Custom Threshold Setting 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Custom Threshold Setting 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Adjustment Code Processing - Variant 27 	 Id: TC2563 	 Description: Verify system handles invalid or missing data during Adjustment Code Processing 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Adjustment Code Processing 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Trend Anomaly Alert - Variant 19 	 Id: TC2222 	 Description: Verify dashboard UI component displays output from Trend Anomaly Alert 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Trend Anomaly Alert 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Feature Attribution UI - Variant 7 	 Id: TC1752 	 Description: Verify accuracy and SLA metrics for Feature Attribution UI predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Feature Attribution UI 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Trend Anomaly Alert - Variant 28 	 Id: TC2582 	 Description: Verify dashboard UI component displays output from Trend Anomaly Alert 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Trend Anomaly Alert 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: High Value Claim Audit Trigger - Variant 21 	 Id: TC2333 	 Description: Verify adjudication engine logic for High Value Claim Audit Trigger 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing High Value Claim Audit Trigger into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Batch Claim Ingestion - Variant 14 	 Id: TC2051 	 Description: Verify system handles invalid or missing data during Batch Claim Ingestion 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Batch Claim Ingestion 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Retraining Trigger - Variant 4 	 Id: TC1660 	 Description: Verify accuracy and SLA metrics for Model Retraining Trigger predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Retraining Trigger 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: No Significant Insights 	 Id: TC035 	 Description: Verify dashboard fallback layout when no significant data trends are detected 	 Precondition: Product metrics reflect flat historical norms with zero variance anomalies. 	 Test Step: 1 	 Test Step Description: Load product management analytics dashboard view. 	 Test Step Expected Result: Dashboard cleanly outputs system fallback status notification layout stating: 'No significant insights found'.</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Unusual Billing Pattern Flag - Variant 11 	 Id: TC1934 	 Description: Verify dashboard UI component displays output from Unusual Billing Pattern Flag 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Unusual Billing Pattern Flag 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Explanation Tooltip Generation - Variant 14 	 Id: TC2042 	 Description: Verify dashboard UI component displays output from Explanation Tooltip Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Explanation Tooltip Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 27 	 Id: TC2565 	 Description: Verify adjudication engine logic for Provider NPI Verification 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Provider NPI Verification into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Bundled Service Deduction - Variant 27 	 Id: TC2567 	 Description: Verify system handles invalid or missing data during Bundled Service Deduction 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Bundled Service Deduction 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Out-of-Network Coinsurance - Variant 22 	 Id: TC2343 	 Description: Verify system handles invalid or missing data during Out-of-Network Coinsurance 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Out-of-Network Coinsurance 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 18 	 Id: TC2190 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 23 	 Id: TC2398 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 1 	 Id: TC1510 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Timely Filing Limit Edge - Variant 25 	 Id: TC2477 	 Description: Verify adjudication engine logic for Timely Filing Limit Edge 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Timely Filing Limit Edge into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Anomaly Detection Alert 	 Id: TC002 	 Description: Verify alert generation SLA when a product metric deviates from historical distribution boundaries 	 Precondition: Pre-trained predictive model cores are fully operational. 	 Test Step: 1 	 Test Step Description: Inject anomalous sample data stream into active processing queue paths. 	 Test Step Expected Result: AI processing layer intercepts structural boundary exception and sends a system alert UI notification within 2 seconds.</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 2 	 Id: TC1550 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 20 	 Id: TC2269 	 Description: Verify adjudication engine logic for Claim Line Item Split 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Claim Line Item Split into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Patient Risk Stratification - Variant 21 	 Id: TC2336 	 Description: Verify accuracy and SLA metrics for Patient Risk Stratification predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Patient Risk Stratification 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Timely Filing Limit Edge - Variant 11 	 Id: TC1917 	 Description: Verify adjudication engine logic for Timely Filing Limit Edge 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Timely Filing Limit Edge into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Data Pipeline Health Monitor - Variant 17 	 Id: TC2172 	 Description: Verify accuracy and SLA metrics for Data Pipeline Health Monitor predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Data Pipeline Health Monitor 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: In-Network Co-pay Calculation - Variant 28 	 Id: TC2581 	 Description: Verify adjudication engine logic for In-Network Co-pay Calculation 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing In-Network Co-pay Calculation into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 16 	 Id: TC2108 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Cost Spike Detection - Variant 25 	 Id: TC2466 	 Description: Verify dashboard UI component displays output from Cost Spike Detection 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Cost Spike Detection 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Custom Threshold Setting - Variant 26 	 Id: TC2526 	 Description: Verify dashboard UI component displays output from Custom Threshold Setting 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Custom Threshold Setting 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 27 	 Id: TC2549 	 Description: Verify adjudication engine logic for Claim Line Item Split 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Claim Line Item Split into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Unusual Billing Pattern Flag - Variant 16 	 Id: TC2134 	 Description: Verify dashboard UI component displays output from Unusual Billing Pattern Flag 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Unusual Billing Pattern Flag 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 27 	 Id: TC2550 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Recommendation Engine Ranking - Variant 12 	 Id: TC1950 	 Description: Verify dashboard UI component displays output from Recommendation Engine Ranking 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Recommendation Engine Ranking 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 18 	 Id: TC2188 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Batch Model Scoring - Variant 11 	 Id: TC1920 	 Description: Verify accuracy and SLA metrics for Batch Model Scoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Batch Model Scoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Out-of-Network Coinsurance - Variant 12 	 Id: TC1943 	 Description: Verify system handles invalid or missing data during Out-of-Network Coinsurance 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Out-of-Network Coinsurance 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Unusual Billing Pattern Flag - Variant 21 	 Id: TC2334 	 Description: Verify dashboard UI component displays output from Unusual Billing Pattern Flag 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Unusual Billing Pattern Flag 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Trend Anomaly Alert - Variant 17 	 Id: TC2142 	 Description: Verify dashboard UI component displays output from Trend Anomaly Alert 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Trend Anomaly Alert 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: In-Network Co-pay Calculation - Variant 20 	 Id: TC2261 	 Description: Verify adjudication engine logic for In-Network Co-pay Calculation 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing In-Network Co-pay Calculation into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Feature Attribution UI - Variant 3 	 Id: TC1592 	 Description: Verify accuracy and SLA metrics for Feature Attribution UI predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Feature Attribution UI 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Automated Summary Generation - Variant 11 	 Id: TC1938 	 Description: Verify dashboard UI component displays output from Automated Summary Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Automated Summary Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Retraining Trigger - Variant 24 	 Id: TC2460 	 Description: Verify accuracy and SLA metrics for Model Retraining Trigger predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Retraining Trigger 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 4 	 Id: TC1648 	 Description: Verify accuracy and SLA metrics for Historical Baseline Comparison predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Historical Baseline Comparison 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Tax ID Validation - Variant 23 	 Id: TC2415 	 Description: Verify system handles invalid or missing data during Tax ID Validation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Tax ID Validation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Duplicate Claim Rejection - Variant 21 	 Id: TC2315 	 Description: Verify system handles invalid or missing data during Duplicate Claim Rejection 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Duplicate Claim Rejection 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 26 	 Id: TC2518 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Out-of-Network Coinsurance - Variant 24 	 Id: TC2423 	 Description: Verify system handles invalid or missing data during Out-of-Network Coinsurance 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Out-of-Network Coinsurance 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Corrected Claim Resubmission - Variant 20 	 Id: TC2297 	 Description: Verify adjudication engine logic for Corrected Claim Resubmission 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Corrected Claim Resubmission into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Pre-authorization Check - Variant 19 	 Id: TC2225 	 Description: Verify adjudication engine logic for Pre-authorization Check 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Pre-authorization Check into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Cost Spike Detection - Variant 7 	 Id: TC1746 	 Description: Verify dashboard UI component displays output from Cost Spike Detection 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Cost Spike Detection 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Duplicate Claim Rejection - Variant 29 	 Id: TC2635 	 Description: Verify system handles invalid or missing data during Duplicate Claim Rejection 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Duplicate Claim Rejection 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: High Value Claim Audit Trigger - Variant 10 	 Id: TC1893 	 Description: Verify adjudication engine logic for High Value Claim Audit Trigger 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing High Value Claim Audit Trigger into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Batch Claim Ingestion - Variant 27 	 Id: TC2571 	 Description: Verify system handles invalid or missing data during Batch Claim Ingestion 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Batch Claim Ingestion 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Pre-authorization Check - Variant 16 	 Id: TC2105 	 Description: Verify adjudication engine logic for Pre-authorization Check 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Pre-authorization Check into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Denial Code ERR-ENR-02 - Variant 9 	 Id: TC1841 	 Description: Verify adjudication engine logic for Denial Code ERR-ENR-02 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Denial Code ERR-ENR-02 into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Out-of-Network Coinsurance - Variant 23 	 Id: TC2383 	 Description: Verify system handles invalid or missing data during Out-of-Network Coinsurance 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Out-of-Network Coinsurance 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Diagnosis Code Validation - Variant 23 	 Id: TC2391 	 Description: Verify system handles invalid or missing data during Diagnosis Code Validation 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Diagnosis Code Validation 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Provider NPI Verification - Variant 18 	 Id: TC2205 	 Description: Verify adjudication engine logic for Provider NPI Verification 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Provider NPI Verification into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Retraining Trigger - Variant 25 	 Id: TC2500 	 Description: Verify accuracy and SLA metrics for Model Retraining Trigger predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Retraining Trigger 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Maximum Out-of-Pocket Cap - Variant 25 	 Id: TC2489 	 Description: Verify adjudication engine logic for Maximum Out-of-Pocket Cap 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Maximum Out-of-Pocket Cap into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Claim Line Item Split - Variant 22 	 Id: TC2349 	 Description: Verify adjudication engine logic for Claim Line Item Split 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Claim Line Item Split into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Predictive No-Show Score - Variant 22 	 Id: TC2344 	 Description: Verify accuracy and SLA metrics for Predictive No-Show Score predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Predictive No-Show Score 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Patient Risk Stratification - Variant 26 	 Id: TC2536 	 Description: Verify accuracy and SLA metrics for Patient Risk Stratification predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Patient Risk Stratification 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Bundled Service Deduction - Variant 22 	 Id: TC2367 	 Description: Verify system handles invalid or missing data during Bundled Service Deduction 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Bundled Service Deduction 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Confidence Threshold Filter - Variant 21 	 Id: TC2316 	 Description: Verify accuracy and SLA metrics for Confidence Threshold Filter predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Confidence Threshold Filter 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Cost Spike Detection - Variant 2 	 Id: TC1546 	 Description: Verify dashboard UI component displays output from Cost Spike Detection 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Cost Spike Detection 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Historical Baseline Comparison - Variant 2 	 Id: TC1568 	 Description: Verify accuracy and SLA metrics for Historical Baseline Comparison predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Historical Baseline Comparison 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Denial Code ERR-ENR-02 - Variant 6 	 Id: TC1721 	 Description: Verify adjudication engine logic for Denial Code ERR-ENR-02 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Denial Code ERR-ENR-02 into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: In-Network Co-pay Calculation - Variant 23 	 Id: TC2381 	 Description: Verify adjudication engine logic for In-Network Co-pay Calculation 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing In-Network Co-pay Calculation into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Real-time Stream Ingestion - Variant 20 	 Id: TC2274 	 Description: Verify dashboard UI component displays output from Real-time Stream Ingestion 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Real-time Stream Ingestion 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Retraining Trigger - Variant 18 	 Id: TC2220 	 Description: Verify accuracy and SLA metrics for Model Retraining Trigger predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Retraining Trigger 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Automated Summary Generation - Variant 18 	 Id: TC2218 	 Description: Verify dashboard UI component displays output from Automated Summary Generation 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Automated Summary Generation 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Maximum Out-of-Pocket Cap - Variant 1 	 Id: TC1529 	 Description: Verify adjudication engine logic for Maximum Out-of-Pocket Cap 	 Precondition: Claim adjudication rules engine initialized. 	 Test Step: 1 	 Test Step Description: Ingest synthetic claim payload testing Maximum Out-of-Pocket Cap into the engine 	 Test Step Expected Result: Adjudication engine applies correct formula and outputs calculated totals.</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Real-time Stream Ingestion - Variant 27 	 Id: TC2554 	 Description: Verify dashboard UI component displays output from Real-time Stream Ingestion 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for Real-time Stream Ingestion 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: False Positive Feedback Loop - Variant 25 	 Id: TC2478 	 Description: Verify dashboard UI component displays output from False Positive Feedback Loop 	 Precondition: Historical baseline metrics ingested and indexed. 	 Test Step: 1 	 Test Step Description: Trigger dashboard refresh and monitor response latency for False Positive Feedback Loop 	 Test Step Expected Result: Visualization widget renders top trends with accurate confidence scores.</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Retraining Trigger - Variant 22 	 Id: TC2380 	 Description: Verify accuracy and SLA metrics for Model Retraining Trigger predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Retraining Trigger 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Primary vs Secondary Payer - Variant 26 	 Id: TC2519 	 Description: Verify system handles invalid or missing data during Primary vs Secondary Payer 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Primary vs Secondary Payer 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1573 	 Module: AI Insights &amp; Anomaly Detection 	 Name: Model Drift Monitoring - Variant 24 	 Id: TC2428 	 Description: Verify accuracy and SLA metrics for Model Drift Monitoring predictive execution 	 Precondition: Model checkpoint v2.4 loaded in runtime environment. 	 Test Step: 1 	 Test Step Description: Interact with AI insight card component for Model Drift Monitoring 	 Test Step Expected Result: Explanation model outputs clear feature contribution breakdown.</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Work Item ID: 1572 	 Module: Claims Adjudication 	 Name: Duplicate Claim Rejection - Variant 25 	 Id: TC2475 	 Description: Verify system handles invalid or missing data during Duplicate Claim Rejection 	 Precondition: Inbound EDI 837 claim processing queue online. 	 Test Step: 1 	 Test Step Description: Submit claim batch containing edge case scenarios for Duplicate Claim Rejection 	 Test Step Expected Result: System flags anomaly and routed claim to review queue instantly.</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/text-content.xlsx
+++ b/text-content.xlsx
@@ -462,78 +462,1683 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Scenario ID</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>User Story ID</t>
+          <t>Scenario Title</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Test Case ID</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Test Case Title</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Automation Feasible</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Step #</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Test Step Description</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>TC001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>US32275</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Login Page</t>
+          <t>Plan Recommendation</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Verify side-by-side plan comparison</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>User is logged into the CareSource enrollment portal and has completed the health needs questionnaire</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>User with completed profile and at least two recommended plans</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>System displays side-by-side comparison of at least two plans highlighting premiums, deductibles, co-pays, out-of-pocket maximums, and coverage for specified medications and doctors</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US-002</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>User Stats</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Review plan features and select a plan</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Selected plan is highlighted and user can proceed to enrollment</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TC002</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>US32275</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Verify navigation to enrollment after plan selection</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>User is on the plan comparison page</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>User with at least one recommended plan</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Select a plan and click 'Enroll'</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>System transitions to the enrollment process with the chosen plan pre-selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>TC003</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>US32275</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Negative - No recommended plans</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>User has completed health needs but no plans match criteria</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>User with uncommon criteria resulting in no matches</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>System displays a message: "No plans match your criteria. Please adjust your preferences."</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>TC004</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>US32275</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Edge - Maximum number of plans</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>User qualifies for 10+ plans</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>User with broad criteria resulting in maximum recommendations</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>System displays all recommended plans in a scrollable, readable format without UI breakage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TC005</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Verify member can input medications and providers</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Medication: Metformin 500mg, Provider: Dr. Smith</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to health needs input page</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>System displays input fields for medications and providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Enter medication and provider information and submit</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>System accepts input, validates data, and confirms successful entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TC006</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Verify financial preference input</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Premium: $200, Deductible: $1000, OOP Max: $5000</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to financial preferences section</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>System displays fields for premium, deductible, and out-of-pocket maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Enter preferences and submit</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>System saves preferences and updates recommendation criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TC007</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Negative - Invalid medication entry</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Medication: "" (blank entry)</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Leave medication field blank and submit</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>System displays error: "Medication name required"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TC008</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Edge - Large medication list</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Medication: 20+ entries</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Enter 20+ medications and submit</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>System accepts all entries and processes recommendations without error</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TC009</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>US32273</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Verify guided workflow for plan selection</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Health: Asthma, PCP: Dr. Lee, Premium: $150</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Start guided enrollment</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>System prompts for health data, provider, and financial preferences in sequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Complete all steps and submit</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>System generates and displays personalized plan recommendations with comparison tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TC010</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>US32273</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Negative - Missing required fields</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Omit required health data</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Attempt to proceed without entering all required fields</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>System displays validation errors for missing fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TC011</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>US32273</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Edge - Extreme cost preferences</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Premium: $0, Deductible: $0</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Enter extreme values and submit</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>System processes and displays only plans meeting criteria, or a message if none available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TC012</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Verify demographic and health needs input</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Age: 40, Location: OH, Doctor: Dr. Adams, Medication: Lisinopril</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to demographic input page</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>System displays fields for age, location, doctors, medications</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Enter data and submit</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>System validates and accepts input, proceeding to recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TC013</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Negative - Invalid age</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Age: -1</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Enter invalid age and submit</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>System displays error: "Invalid age"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TC014</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Edge - Maximum field length</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Doctor name: 100+ characters</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Enter maximum length for doctor name and submit</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>System accepts or displays appropriate error without crashing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TC015</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>US32306</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Verify profile view</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>User with profile data</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to profile page</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>System displays correct profile information</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TC016</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>US32307</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Verify settings update</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>New notification preference</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Go to settings, change preference, save</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>System updates and confirms setting change</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TC017</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>US32308</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Transaction History</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Verify transaction history view</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>User with transaction history</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to transaction history</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>System displays all past transactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TC018</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>US32309</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Search and Filter</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Verify data search and filter</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Search: "Diabetes", Filter: Date range</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Enter search term and filter</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>System returns correct filtered data</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TC019</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>US32310</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Export Reports</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Verify report export</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Report: Claims</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Click export on claims report</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>System downloads report in selected format</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TC020</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>US32311</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>User Permissions</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Verify permission management</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Admin user logged in</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Assign 'Editor' to user X</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to permissions, assign role</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>System saves and reflects new permission</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TC021</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>US32312</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>System Logs</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Verify system log view</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Admin user logged in</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Any log record</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to system logs</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>System displays logs with timestamp, user, action</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TC022</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>US32304</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Password Reset</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Verify password reset</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>User on login page</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Registered email</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Click 'Forgot Password', enter email</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>System sends reset link to email</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>TC023</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>US32305</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Two-Factor Authentication</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Verify 2FA enablement</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Valid phone number</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Navigate to security, enable 2FA</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>System sends code and confirms setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TC024</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>US32303</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Verify email login</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>User is registered</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Valid email/password</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Enter credentials, click login</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>System authenticates and redirects to dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TC025</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>US32983</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>NEW STORY TETS</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Basic smoke test</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>System available</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Access feature</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Feature loads without error</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TC026</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>US32744</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>member 1</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Basic smoke test</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>System available</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Access feature</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Feature loads without error</t>
         </is>
       </c>
     </row>
